--- a/2026 부트캠프 커리큘럼 및 일정표.xlsx
+++ b/2026 부트캠프 커리큘럼 및 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/limcw/Documents/2026-yonsei-education/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D427E83-AA6D-A545-8F58-C220169672B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181860CF-CC1D-6443-8425-46308A7EAB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="부트캠프 일정표" sheetId="3" r:id="rId1"/>
@@ -132,10 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>의학연구 위한 기초통계(Table 1), 회귀/생존분석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>통계이론</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -200,10 +196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">실습: RCT 예시데이터와 R/AI agent 이용하여 논문의 분석결과 재현하고, 발표슬라이드/웹 애플리케이션으로 만들기 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>슬라이드, 분석웹 만들기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,10 +213,6 @@
   </si>
   <si>
     <t>의생명연구실 강사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">quarto markdown 활용하여 분석결과를 슬라이드로 만들기, Shiny 로 분석웹 만들기  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -302,10 +290,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가능도(likelihood), 정규분포, RCT에 필요한 샘플수 계산, 생존분석심화(비례위험, 층화/혼합, Landmark) -&gt; 심화는 뺌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>의사의 길: 나만의 특이점을 찾아서 -&gt; https://jinseob2kim.github.io/lecture-general/ishs/#8 (revealjs로 변경)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -335,6 +319,23 @@
   </si>
   <si>
     <t>R 기초 &amp;  AI agent 설치 -&gt; https://jinseob2kim.github.io/lecture-general/claude_code_r/#/title-slide -&gt;  이걸 codex + 터미널 설치로 변경. MAC, Windows 모두 지원해야 함. + api key 당일 안내하도록 비워두기.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의학연구 위한 기초통계(Table 1), 회귀/생존분석 -&gt; 링크 걸기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가능도(likelihood), 정규분포, RCT에 필요한 샘플수 계산 -&gt; 바이오헬스규제과학과에 있다. 심화는 뺌      , 
+생존분석심화(비례위험, 층화/혼합, Landmark) -&gt; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quarto markdown 활용하여 분석결과를 슬라이드로 만들기-&gt;기초 설명하고 이건 따라해보기., Shiny 로 분석웹 만들기-&gt;이건 그냥 보여주기만 할거라고 하심</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실습: RCT 예시데이터와 R/AI agent 이용하여 논문의 분석결과 재현하고, 발표슬라이드/웹 애플리케이션으로 만들기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -400,7 +401,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +447,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -884,6 +891,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,13 +1129,13 @@
   <sheetData>
     <row r="1" spans="1:24" s="44" customFormat="1" ht="16" customHeight="1">
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="47"/>
     </row>
     <row r="2" spans="1:24" s="44" customFormat="1" ht="65.5" customHeight="1">
       <c r="B2" s="59" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
@@ -1225,7 +1236,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>10</v>
@@ -1258,16 +1269,16 @@
         <v>9</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>31</v>
+      <c r="F7" s="70" t="s">
+        <v>76</v>
       </c>
       <c r="G7" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I7" s="20" t="s">
         <v>10</v>
@@ -1335,16 +1346,16 @@
         <v>9</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G9" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I9" s="20" t="s">
         <v>10</v>
@@ -1378,13 +1389,13 @@
       </c>
       <c r="E10" s="64"/>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="27" t="s">
         <v>29</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>10</v>
@@ -1418,13 +1429,13 @@
       </c>
       <c r="E11" s="64"/>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="27" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I11" s="20" t="s">
         <v>10</v>
@@ -1458,13 +1469,13 @@
       </c>
       <c r="E12" s="65"/>
       <c r="F12" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" s="52" t="s">
         <v>29</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I12" s="28" t="s">
         <v>10</v>
@@ -1516,7 +1527,7 @@
     <row r="14" spans="1:24" ht="15.75" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>8</v>
@@ -1525,16 +1536,16 @@
         <v>9</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" s="15" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>10</v>
@@ -1567,16 +1578,16 @@
         <v>9</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
-      <c r="F15" s="36" t="s">
-        <v>71</v>
+      <c r="F15" s="71" t="s">
+        <v>77</v>
       </c>
       <c r="G15" s="27" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I15" s="20" t="s">
         <v>10</v>
@@ -1635,7 +1646,7 @@
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:24" ht="15.75" customHeight="1">
+    <row r="17" spans="1:24" ht="28">
       <c r="A17" s="7"/>
       <c r="B17" s="61"/>
       <c r="C17" s="20" t="s">
@@ -1645,16 +1656,16 @@
         <v>9</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
-      <c r="F17" s="36" t="s">
-        <v>52</v>
+      <c r="F17" s="71" t="s">
+        <v>78</v>
       </c>
       <c r="G17" s="27" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I17" s="20" t="s">
         <v>10</v>
@@ -1687,16 +1698,16 @@
         <v>9</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
-      <c r="F18" s="36" t="s">
-        <v>46</v>
+      <c r="F18" s="71" t="s">
+        <v>79</v>
       </c>
       <c r="G18" s="27" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>10</v>
@@ -1731,14 +1742,14 @@
       <c r="E19" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>72</v>
+      <c r="F19" s="70" t="s">
+        <v>68</v>
       </c>
       <c r="G19" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I19" s="20" t="s">
         <v>10</v>
@@ -1774,13 +1785,13 @@
         <v>20</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I20" s="28" t="s">
         <v>10</v>
@@ -1832,7 +1843,7 @@
     <row r="22" spans="1:24" ht="14">
       <c r="A22" s="7"/>
       <c r="B22" s="60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>8</v>
@@ -1841,16 +1852,16 @@
         <v>9</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="49" t="s">
@@ -1881,16 +1892,16 @@
         <v>9</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I23" s="20"/>
       <c r="J23" s="50" t="s">
@@ -1955,16 +1966,16 @@
         <v>9</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G25" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I25" s="20"/>
       <c r="J25" s="50" t="s">
@@ -1996,13 +2007,13 @@
       </c>
       <c r="E26" s="67"/>
       <c r="F26" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G26" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I26" s="20"/>
       <c r="J26" s="50" t="s">
@@ -2033,16 +2044,16 @@
         <v>9</v>
       </c>
       <c r="E27" s="67" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>77</v>
+      <c r="F27" s="70" t="s">
+        <v>73</v>
       </c>
       <c r="G27" s="27" t="s">
         <v>30</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I27" s="20"/>
       <c r="J27" s="50" t="s">
@@ -2073,14 +2084,14 @@
         <v>18</v>
       </c>
       <c r="E28" s="68"/>
-      <c r="F28" s="5" t="s">
-        <v>78</v>
+      <c r="F28" s="70" t="s">
+        <v>74</v>
       </c>
       <c r="G28" s="52" t="s">
         <v>30</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I28" s="28"/>
       <c r="J28" s="53" t="s">
@@ -2130,7 +2141,7 @@
     <row r="30" spans="1:24" ht="15.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>8</v>
@@ -2139,16 +2150,16 @@
         <v>9</v>
       </c>
       <c r="E30" s="66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H30" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="49" t="s">
@@ -2180,13 +2191,13 @@
       </c>
       <c r="E31" s="67"/>
       <c r="F31" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G31" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I31" s="20"/>
       <c r="J31" s="50" t="s">
@@ -2251,16 +2262,16 @@
         <v>9</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I33" s="20"/>
       <c r="J33" s="50" t="s">
@@ -2291,16 +2302,16 @@
         <v>9</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="50" t="s">
@@ -2331,16 +2342,16 @@
         <v>9</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G35" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I35" s="20"/>
       <c r="J35" s="50" t="s">
@@ -2374,10 +2385,10 @@
         <v>19</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H36" s="28" t="s">
         <v>30</v>
@@ -2430,7 +2441,7 @@
     <row r="38" spans="1:24" ht="14">
       <c r="A38" s="7"/>
       <c r="B38" s="60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>8</v>
@@ -2442,13 +2453,13 @@
         <v>23</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G38" s="55" t="s">
         <v>30</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I38" s="15"/>
       <c r="J38" s="49"/>
@@ -2480,13 +2491,13 @@
         <v>23</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G39" s="56" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I39" s="27"/>
       <c r="J39" s="50"/>
@@ -2553,7 +2564,7 @@
         <v>30</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I41" s="27"/>
       <c r="J41" s="50"/>
@@ -2588,7 +2599,7 @@
         <v>30</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I42" s="27"/>
       <c r="J42" s="50"/>
@@ -2624,7 +2635,7 @@
         <v>30</v>
       </c>
       <c r="H43" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I43" s="28"/>
       <c r="J43" s="53"/>
